--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>defect_desc</t>
   </si>
@@ -128,6 +128,9 @@
   </si>
   <si>
     <t>群暗点</t>
+  </si>
+  <si>
+    <t>2nit亮点</t>
   </si>
 </sst>
 </file>
@@ -485,7 +488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -501,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>9.656909325484198E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -509,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003070897165503975</v>
+        <v>0.0003894638434403332</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -517,7 +520,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001317202431996045</v>
+        <v>0.0013971115697952</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -525,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0001912068046445871</v>
+        <v>0.0002039287065241991</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -533,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002263579545893496</v>
+        <v>0.002284801233488773</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -541,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>2.027950958351682E-05</v>
+        <v>1.919329002580698E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -549,7 +552,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>9.656909325484198E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -557,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.0001110544572430683</v>
+        <v>0.000111960858483874</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -565,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2.027950958351682E-05</v>
+        <v>2.239217169677481E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -573,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>6.759836527838938E-05</v>
+        <v>6.95756763435503E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -581,7 +584,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2.800503704390417E-05</v>
+        <v>2.799021462096851E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -589,7 +592,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>4.538747382977573E-05</v>
+        <v>3.998602088709787E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -605,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>8.691218392935777E-06</v>
+        <v>1.199580626612936E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -613,7 +616,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>1.641674585332314E-05</v>
+        <v>2.399161253225872E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -621,7 +624,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.00413701995503743</v>
+        <v>0.004033789787090433</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -629,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002174735980099041</v>
+        <v>0.002188834783359737</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -637,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.0001129858391081651</v>
+        <v>8.63698051161314E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -645,7 +648,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.158829119058104E-05</v>
+        <v>1.199580626612936E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -653,7 +656,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>9.656909325484198E-07</v>
+        <v>1.599440835483915E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -661,7 +664,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>5.118161942506625E-05</v>
+        <v>6.637679467258246E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -669,7 +672,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>9.656909325484198E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -677,7 +680,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>8.594649299680936E-05</v>
+        <v>9.996505221774468E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -685,7 +688,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>4.828454662742099E-06</v>
+        <v>3.998602088709787E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -693,7 +696,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0003872420639519163</v>
+        <v>0.0004478434339354962</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -701,7 +704,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>6.759836527838938E-06</v>
+        <v>5.598042924193702E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -709,7 +712,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>9.656909325484198E-07</v>
+        <v>4.798322506451744E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -717,7 +720,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>1.93138186509684E-06</v>
+        <v>1.599440835483915E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -725,7 +728,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006672924343909581</v>
+        <v>0.0006517721404596953</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -733,7 +736,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>5.794145595290518E-06</v>
+        <v>7.197483759677616E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -741,7 +744,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>9.656909325484198E-06</v>
+        <v>8.796924595161532E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -749,7 +752,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>1.738243678587155E-05</v>
+        <v>1.519468793709719E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -757,7 +760,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.001775905624956544</v>
+        <v>0.002048883710254895</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -765,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>8.691218392935777E-06</v>
+        <v>9.596645012903489E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -773,7 +776,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009994901151876145</v>
+        <v>0.0009604642217080909</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -781,7 +784,15 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004061696062298653</v>
+        <v>0.004196932752309792</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38">
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.997204177419574E-07</v>
+        <v>7.997223364048003E-07</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -512,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003894638434403332</v>
+        <v>0.0003894647778291377</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -520,7 +520,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.0013971115697952</v>
+        <v>0.001397114921699186</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002039287065241991</v>
+        <v>0.0002039291957832241</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -536,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002284801233488773</v>
+        <v>0.002284806715108514</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.919329002580698E-05</v>
+        <v>1.919333607371521E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -552,7 +552,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>7.997204177419574E-07</v>
+        <v>7.997223364048003E-07</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -560,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.000111960858483874</v>
+        <v>0.000111961127096672</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2.239217169677481E-05</v>
+        <v>2.239222541933441E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -576,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>6.95756763435503E-05</v>
+        <v>6.957584326721762E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -584,7 +584,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2.799021462096851E-05</v>
+        <v>2.799028177416801E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -592,7 +592,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3.998602088709787E-05</v>
+        <v>3.998611682024001E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -608,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.199580626612936E-05</v>
+        <v>1.1995835046072E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -616,7 +616,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.399161253225872E-05</v>
+        <v>2.399167009214401E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -624,7 +624,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004033789787090433</v>
+        <v>0.004033799464825813</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -632,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002188834783359737</v>
+        <v>0.002188840034739938</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -640,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>8.63698051161314E-05</v>
+        <v>8.637001233171843E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -648,7 +648,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.199580626612936E-05</v>
+        <v>1.1995835046072E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -656,7 +656,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>1.599440835483915E-06</v>
+        <v>1.599444672809601E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -664,7 +664,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>6.637679467258246E-05</v>
+        <v>6.637695392159843E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -672,7 +672,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>7.997204177419574E-07</v>
+        <v>7.997223364048003E-07</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -680,7 +680,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>9.996505221774468E-05</v>
+        <v>9.996529205060004E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -688,7 +688,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>3.998602088709787E-06</v>
+        <v>3.998611682024001E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -696,7 +696,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004478434339354962</v>
+        <v>0.0004478445083866881</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -704,7 +704,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>5.598042924193702E-06</v>
+        <v>5.598056354833602E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -712,7 +712,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4.798322506451744E-06</v>
+        <v>4.798334018428802E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -720,7 +720,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>1.599440835483915E-06</v>
+        <v>1.599444672809601E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -728,7 +728,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006517721404596953</v>
+        <v>0.0006517737041699122</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -736,7 +736,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.197483759677616E-06</v>
+        <v>7.197501027643203E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -744,7 +744,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.796924595161532E-06</v>
+        <v>8.796945700452803E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -752,7 +752,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>1.519468793709719E-05</v>
+        <v>1.519472439169121E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -760,7 +760,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.002048883710254895</v>
+        <v>0.002048888625869098</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -768,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>9.596645012903489E-06</v>
+        <v>9.596668036857604E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -776,7 +776,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009604642217080909</v>
+        <v>0.0009604665260221651</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -784,7 +784,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004196932752309792</v>
+        <v>0.004196942821452392</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -792,7 +792,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>7.997204177419574E-07</v>
+        <v>7.997223364048003E-07</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -504,7 +504,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.997223364048003E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -512,7 +512,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003894647778291377</v>
+        <v>0.0003894638434403332</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -520,7 +520,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001397114921699186</v>
+        <v>0.0013971115697952</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -528,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002039291957832241</v>
+        <v>0.0002039287065241991</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -536,7 +536,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002284806715108514</v>
+        <v>0.002284801233488773</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.919333607371521E-05</v>
+        <v>1.919329002580698E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -552,7 +552,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>7.997223364048003E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -560,7 +560,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.000111961127096672</v>
+        <v>0.000111960858483874</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -568,7 +568,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2.239222541933441E-05</v>
+        <v>2.239217169677481E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -576,7 +576,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>6.957584326721762E-05</v>
+        <v>6.95756763435503E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -584,7 +584,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2.799028177416801E-05</v>
+        <v>2.799021462096851E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -592,7 +592,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3.998611682024001E-05</v>
+        <v>3.998602088709787E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -608,7 +608,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.1995835046072E-05</v>
+        <v>1.199580626612936E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -616,7 +616,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.399167009214401E-05</v>
+        <v>2.399161253225872E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -624,7 +624,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004033799464825813</v>
+        <v>0.004033789787090433</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -632,7 +632,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002188840034739938</v>
+        <v>0.002188834783359737</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -640,7 +640,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>8.637001233171843E-05</v>
+        <v>8.63698051161314E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -648,7 +648,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.1995835046072E-05</v>
+        <v>1.199580626612936E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -656,7 +656,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>1.599444672809601E-06</v>
+        <v>1.599440835483915E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -664,7 +664,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>6.637695392159843E-05</v>
+        <v>6.637679467258246E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -672,7 +672,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>7.997223364048003E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -680,7 +680,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>9.996529205060004E-05</v>
+        <v>9.996505221774468E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -688,7 +688,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>3.998611682024001E-06</v>
+        <v>3.998602088709787E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -696,7 +696,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004478445083866881</v>
+        <v>0.0004478434339354962</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -704,7 +704,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>5.598056354833602E-06</v>
+        <v>5.598042924193702E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -712,7 +712,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4.798334018428802E-06</v>
+        <v>4.798322506451744E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -720,7 +720,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>1.599444672809601E-06</v>
+        <v>1.599440835483915E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -728,7 +728,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006517737041699122</v>
+        <v>0.0006517721404596953</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -736,7 +736,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.197501027643203E-06</v>
+        <v>7.197483759677616E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -744,7 +744,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.796945700452803E-06</v>
+        <v>8.796924595161532E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -752,7 +752,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>1.519472439169121E-05</v>
+        <v>1.519468793709719E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -760,7 +760,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.002048888625869098</v>
+        <v>0.002048883710254895</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -768,7 +768,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>9.596668036857604E-06</v>
+        <v>9.596645012903489E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -776,7 +776,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009604665260221651</v>
+        <v>0.0009604642217080909</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -784,7 +784,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004196942821452392</v>
+        <v>0.004196932752309792</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -792,7 +792,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>7.997223364048003E-07</v>
+        <v>7.997204177419574E-07</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>defect_desc</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>2nit亮点</t>
+  </si>
+  <si>
+    <t>TP复测NG</t>
   </si>
 </sst>
 </file>
@@ -488,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -504,7 +507,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.997204177419574E-07</v>
+        <v>7.997172199910112E-07</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -512,7 +515,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003894638434403332</v>
+        <v>0.0003894622861356224</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -520,7 +523,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.0013971115697952</v>
+        <v>0.001397105983324297</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -528,7 +531,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002039287065241991</v>
+        <v>0.0002039278910977078</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -536,7 +539,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002284801233488773</v>
+        <v>0.002284792097514319</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -544,7 +547,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.919329002580698E-05</v>
+        <v>1.919321327978427E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -552,7 +555,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>7.997204177419574E-07</v>
+        <v>7.997172199910112E-07</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -560,7 +563,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.000111960858483874</v>
+        <v>0.0001119604107987416</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -568,7 +571,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2.239217169677481E-05</v>
+        <v>2.239208215974831E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -576,7 +579,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>6.95756763435503E-05</v>
+        <v>6.957539813921798E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -584,7 +587,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2.799021462096851E-05</v>
+        <v>2.799010269968539E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -592,7 +595,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3.998602088709787E-05</v>
+        <v>3.998586099955056E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -608,7 +611,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.199580626612936E-05</v>
+        <v>1.199575829986517E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -616,7 +619,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.399161253225872E-05</v>
+        <v>2.399151659973033E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -624,7 +627,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004033789787090433</v>
+        <v>0.00403377365763466</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -632,7 +635,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002188834783359737</v>
+        <v>0.002189625748335389</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -640,7 +643,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>8.63698051161314E-05</v>
+        <v>8.636945975902921E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -648,7 +651,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.199580626612936E-05</v>
+        <v>1.199575829986517E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -656,7 +659,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>1.599440835483915E-06</v>
+        <v>1.599434439982022E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -664,7 +667,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>6.637679467258246E-05</v>
+        <v>6.637652925925393E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -672,7 +675,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>7.997204177419574E-07</v>
+        <v>7.997172199910112E-07</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -680,7 +683,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>9.996505221774468E-05</v>
+        <v>9.99646524988764E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -688,7 +691,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>3.998602088709787E-06</v>
+        <v>3.998586099955056E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -696,7 +699,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004478434339354962</v>
+        <v>0.0004478416431949662</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -704,7 +707,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>5.598042924193702E-06</v>
+        <v>5.598020539937078E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -712,7 +715,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4.798322506451744E-06</v>
+        <v>4.798303319946067E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -720,7 +723,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>1.599440835483915E-06</v>
+        <v>1.599434439982022E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -728,7 +731,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006517721404596953</v>
+        <v>0.0006517695342926741</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -736,7 +739,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.197483759677616E-06</v>
+        <v>7.197454979919101E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -744,7 +747,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.796924595161532E-06</v>
+        <v>8.796889419901122E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -752,7 +755,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>1.519468793709719E-05</v>
+        <v>1.519462717982921E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -760,7 +763,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.002048883710254895</v>
+        <v>0.00204887551761697</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -768,7 +771,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>9.596645012903489E-06</v>
+        <v>9.596606639892135E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -776,7 +779,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009604642217080909</v>
+        <v>0.0009604603812092044</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -784,7 +787,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004196932752309792</v>
+        <v>0.0041993151221728</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -792,7 +795,15 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>7.997204177419574E-07</v>
+        <v>7.997172199910112E-07</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39">
+        <v>0.0001047629558188225</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>defect_desc</t>
   </si>
@@ -134,6 +134,69 @@
   </si>
   <si>
     <t>TP复测NG</t>
+  </si>
+  <si>
+    <t>G向ELA Mura</t>
+  </si>
+  <si>
+    <t>G向带状Mura</t>
+  </si>
+  <si>
+    <t>G向线状Mura</t>
+  </si>
+  <si>
+    <t>RGB黑斑</t>
+  </si>
+  <si>
+    <t>S向ELA Mura</t>
+  </si>
+  <si>
+    <t>S向带状Mura</t>
+  </si>
+  <si>
+    <t>S向线状Mura</t>
+  </si>
+  <si>
+    <t>右斜黑色带状Mura</t>
+  </si>
+  <si>
+    <t>大圆环Mura</t>
+  </si>
+  <si>
+    <t>孔区跑道Mura</t>
+  </si>
+  <si>
+    <t>左斜黑色带状Mura</t>
+  </si>
+  <si>
+    <t>常亮白斑</t>
+  </si>
+  <si>
+    <t>常暗黑斑Mura</t>
+  </si>
+  <si>
+    <t>流星状划线</t>
+  </si>
+  <si>
+    <t>灰阶块状白斑Mura</t>
+  </si>
+  <si>
+    <t>灰阶小白斑Mura</t>
+  </si>
+  <si>
+    <t>灰阶点状白斑Mura</t>
+  </si>
+  <si>
+    <t>环状Mura</t>
+  </si>
+  <si>
+    <t>白画面黑斑Mura</t>
+  </si>
+  <si>
+    <t>雪花状Mura</t>
+  </si>
+  <si>
+    <t>青/粉斑Mura</t>
   </si>
 </sst>
 </file>
@@ -491,7 +554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B60"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -507,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.997172199910112E-07</v>
+        <v>7.997184990883209E-07</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -515,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003894622861356224</v>
+        <v>0.0003894629090560123</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -523,7 +586,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001397105983324297</v>
+        <v>0.001397108217907297</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -531,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002039278910977078</v>
+        <v>0.0002039282172675218</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -539,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002284792097514319</v>
+        <v>0.002284795751895333</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -547,7 +610,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.919321327978427E-05</v>
+        <v>1.91932439781197E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -555,7 +618,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>7.997172199910112E-07</v>
+        <v>7.997184990883209E-07</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -563,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.0001119604107987416</v>
+        <v>0.0001119605898723649</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -571,7 +634,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2.239208215974831E-05</v>
+        <v>2.239211797447299E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -579,7 +642,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>6.957539813921798E-05</v>
+        <v>6.957550942068392E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -587,7 +650,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2.799010269968539E-05</v>
+        <v>2.799014746809123E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -595,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3.998586099955056E-05</v>
+        <v>3.998592495441604E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -611,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.199575829986517E-05</v>
+        <v>1.199577748632481E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -619,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.399151659973033E-05</v>
+        <v>2.399155497264963E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -627,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.00403377365763466</v>
+        <v>0.00403378010940149</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -635,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002189625748335389</v>
+        <v>0.002189629250503823</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -643,7 +706,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>8.636945975902921E-05</v>
+        <v>8.636959790153866E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -651,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.199575829986517E-05</v>
+        <v>1.199577748632481E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -659,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>1.599434439982022E-06</v>
+        <v>1.599436998176642E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -667,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>6.637652925925393E-05</v>
+        <v>6.637663542433064E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -675,7 +738,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>7.997172199910112E-07</v>
+        <v>7.997184990883209E-07</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -683,7 +746,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>9.99646524988764E-05</v>
+        <v>9.996481238604012E-05</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -691,7 +754,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>3.998586099955056E-06</v>
+        <v>3.998592495441605E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -699,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004478416431949662</v>
+        <v>0.0004478423594894597</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -707,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>5.598020539937078E-06</v>
+        <v>5.598029493618247E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -715,7 +778,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4.798303319946067E-06</v>
+        <v>4.798310994529925E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -723,7 +786,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>1.599434439982022E-06</v>
+        <v>1.599436998176642E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -731,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006517695342926741</v>
+        <v>0.0006517705767569816</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -739,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.197454979919101E-06</v>
+        <v>7.197466491794889E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -747,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.796889419901122E-06</v>
+        <v>8.79690348997153E-06</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -755,7 +818,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>1.519462717982921E-05</v>
+        <v>1.51946514826781E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -763,7 +826,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.00204887551761697</v>
+        <v>0.002048878794664278</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -771,7 +834,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>9.596606639892135E-06</v>
+        <v>9.59662198905985E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -779,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009604603812092044</v>
+        <v>0.0009604619174050734</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -787,7 +850,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.0041993151221728</v>
+        <v>0.004199321838712773</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -795,7 +858,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>7.997172199910112E-07</v>
+        <v>7.997184990883209E-07</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -803,7 +866,175 @@
         <v>39</v>
       </c>
       <c r="B39">
-        <v>0.0001047629558188225</v>
+        <v>0.0001047630395996293</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40">
+        <v>0.003627523111864624</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41">
+        <v>8.477016090336202E-05</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42">
+        <v>3.198873996353284E-06</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>43</v>
+      </c>
+      <c r="B43">
+        <v>1.279549598541313E-05</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44">
+        <v>0.001122005054220914</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45">
+        <v>0.001198778030133393</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46">
+        <v>2.399155497264963E-06</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>47</v>
+      </c>
+      <c r="B47">
+        <v>7.197466491794889E-06</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>48</v>
+      </c>
+      <c r="B48">
+        <v>3.83864879562394E-05</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>49</v>
+      </c>
+      <c r="B49">
+        <v>8.157128690700874E-05</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+      <c r="B50">
+        <v>1.199577748632481E-05</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>51</v>
+      </c>
+      <c r="B51">
+        <v>0.0007013531237004575</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>52</v>
+      </c>
+      <c r="B52">
+        <v>0.002164837977032085</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" t="s">
+        <v>53</v>
+      </c>
+      <c r="B53">
+        <v>4.878282844438758E-05</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" t="s">
+        <v>54</v>
+      </c>
+      <c r="B54">
+        <v>1.599436998176642E-06</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55">
+        <v>7.997184990883209E-07</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>56</v>
+      </c>
+      <c r="B56">
+        <v>1.599436998176642E-06</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57">
+        <v>4.798310994529925E-06</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" t="s">
+        <v>58</v>
+      </c>
+      <c r="B58">
+        <v>0.0003646716355842743</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" t="s">
+        <v>59</v>
+      </c>
+      <c r="B59">
+        <v>8.79690348997153E-06</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>60</v>
+      </c>
+      <c r="B60">
+        <v>7.997184990883209E-07</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>7.997184990883209E-07</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -578,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003894629090560123</v>
+        <v>0.000361735515294789</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -586,7 +586,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001397108217907297</v>
+        <v>0.001426562595528745</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -594,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002039282172675218</v>
+        <v>0.0002114369561230104</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002284795751895333</v>
+        <v>0.002361470582241334</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.91932439781197E-05</v>
+        <v>1.273716603150665E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -618,7 +618,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>7.997184990883209E-07</v>
+        <v>8.032438198420501E-07</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.0001119605898723649</v>
+        <v>8.406529580794391E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -634,7 +634,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>2.239211797447299E-05</v>
+        <v>4.840123091972528E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -642,7 +642,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>6.957550942068392E-05</v>
+        <v>2.037946565041064E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -650,7 +650,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>2.799014746809123E-05</v>
+        <v>4.330636450712262E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3.998592495441604E-05</v>
+        <v>6.368583015753328E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -674,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.199577748632481E-05</v>
+        <v>1.528459923780799E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -682,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.399155497264963E-05</v>
+        <v>3.31166316819173E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -690,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.00403378010940149</v>
+        <v>0.004114104628176649</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -698,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002189629250503823</v>
+        <v>0.002175507958181336</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>8.636959790153866E-05</v>
+        <v>0.0001401088263465732</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -714,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.199577748632481E-05</v>
+        <v>1.273716603150665E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>1.599436998176642E-06</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -730,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>6.637663542433064E-05</v>
+        <v>5.094866412602661E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -738,7 +738,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>7.997184990883209E-07</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -746,7 +746,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>9.996481238604012E-05</v>
+        <v>0.0001579408587906825</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -754,7 +754,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>3.998592495441605E-06</v>
+        <v>1.273716603150665E-05</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -762,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004478423594894597</v>
+        <v>0.0004789174427846502</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -770,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>5.598029493618247E-06</v>
+        <v>1.528459923780799E-05</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -778,7 +778,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4.798310994529925E-06</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -786,7 +786,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>1.599436998176642E-06</v>
+        <v>5.094866412602661E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -794,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006517705767569816</v>
+        <v>0.000647048034400538</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -802,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.197466491794889E-06</v>
+        <v>7.642299618903993E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -810,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>8.79690348997153E-06</v>
+        <v>1.273716603150665E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -818,7 +818,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>1.51946514826781E-05</v>
+        <v>4.075893130082129E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -826,7 +826,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.002048878794664278</v>
+        <v>0.001925859503963806</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -834,7 +834,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>9.59662198905985E-06</v>
+        <v>2.292689885671198E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -842,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009604619174050734</v>
+        <v>0.001021520715726834</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -850,7 +850,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004199321838712773</v>
+        <v>0.004119199494589252</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -858,7 +858,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>7.997184990883209E-07</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -874,7 +874,7 @@
         <v>40</v>
       </c>
       <c r="B40">
-        <v>0.003627523111864624</v>
+        <v>0.003627520210869605</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -882,7 +882,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>8.477016090336202E-05</v>
+        <v>0.0002241741221545171</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -890,7 +890,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>3.198873996353284E-06</v>
+        <v>7.642299618903993E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -898,7 +898,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.279549598541313E-05</v>
+        <v>1.528459923780799E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -906,7 +906,7 @@
         <v>44</v>
       </c>
       <c r="B44">
-        <v>0.001122005054220914</v>
+        <v>0.001122004156933434</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.001198778030133393</v>
+        <v>0.001637999551651756</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46</v>
       </c>
       <c r="B46">
-        <v>2.399155497264963E-06</v>
+        <v>2.40973145952615E-06</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -930,7 +930,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>7.197466491794889E-06</v>
+        <v>7.642299618903993E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -938,7 +938,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>3.83864879562394E-05</v>
+        <v>5.859096374493061E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -946,7 +946,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>8.157128690700874E-05</v>
+        <v>0.0008151786260164258</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -954,7 +954,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>1.199577748632481E-05</v>
+        <v>7.642299618903993E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -962,7 +962,7 @@
         <v>51</v>
       </c>
       <c r="B51">
-        <v>0.0007013531237004575</v>
+        <v>0.0007046961530178994</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -970,7 +970,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.002164837977032085</v>
+        <v>0.003298926002160223</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -978,7 +978,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>4.878282844438758E-05</v>
+        <v>5.859096374493061E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -986,7 +986,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>1.599436998176642E-06</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -994,7 +994,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>7.997184990883209E-07</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>1.599436998176642E-06</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>4.798310994529925E-06</v>
+        <v>5.094866412602661E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.0003646716355842743</v>
+        <v>0.001337402433308199</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>8.79690348997153E-06</v>
+        <v>1.528459923780799E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>7.997184990883209E-07</v>
+        <v>2.547433206301331E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -578,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.000361735515294789</v>
+        <v>0.0003617143221040565</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -586,7 +586,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001426562595528745</v>
+        <v>0.001426479016748392</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -594,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002114369561230104</v>
+        <v>0.0002114245685537795</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002361470582241334</v>
+        <v>0.002374068649302681</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.273716603150665E-05</v>
+        <v>1.273641979239636E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>8.406529580794391E-05</v>
+        <v>8.406037062981596E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -634,7 +634,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4.840123091972528E-05</v>
+        <v>4.839839521110616E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -642,7 +642,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.037946565041064E-05</v>
+        <v>2.037827166783417E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -650,7 +650,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>4.330636450712262E-05</v>
+        <v>4.330382729414762E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>6.368583015753328E-05</v>
+        <v>6.368209896198179E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -674,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.528459923780799E-05</v>
+        <v>1.528370375087563E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -682,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>3.31166316819173E-05</v>
+        <v>3.311469146023053E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -690,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004114104628176649</v>
+        <v>0.004116410876902503</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -698,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002175507958181336</v>
+        <v>0.002183022352416736</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.0001401088263465732</v>
+        <v>0.0001401006177163599</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -714,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.273716603150665E-05</v>
+        <v>1.273641979239636E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -730,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>5.094866412602661E-05</v>
+        <v>5.094567916958543E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -738,7 +738,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -746,7 +746,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0001579408587906825</v>
+        <v>0.0001579316054257148</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -754,7 +754,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1.273716603150665E-05</v>
+        <v>1.273641979239636E-05</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -762,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004789174427846502</v>
+        <v>0.000478889384194103</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -770,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>1.528459923780799E-05</v>
+        <v>1.528370375087563E-05</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -778,7 +778,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -786,7 +786,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>5.094866412602661E-06</v>
+        <v>5.094567916958543E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -794,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.000647048034400538</v>
+        <v>0.0006470101254537349</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -802,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.642299618903993E-06</v>
+        <v>7.641851875437814E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -810,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.273716603150665E-05</v>
+        <v>1.273641979239636E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -818,7 +818,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>4.075893130082129E-05</v>
+        <v>4.075654333566834E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -826,7 +826,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.001925859503963806</v>
+        <v>0.001925746672610329</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -834,7 +834,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>2.292689885671198E-05</v>
+        <v>2.292555562631344E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -842,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.001021520715726834</v>
+        <v>0.001024008151308667</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -850,7 +850,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004119199494589252</v>
+        <v>0.004129147296694899</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -858,7 +858,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -882,7 +882,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.0002241741221545171</v>
+        <v>0.0002241609883461759</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -890,7 +890,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>7.642299618903993E-06</v>
+        <v>7.641851875437814E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -898,7 +898,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.528459923780799E-05</v>
+        <v>1.528370375087563E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.001637999551651756</v>
+        <v>0.001637903585302172</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -930,7 +930,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>7.642299618903993E-06</v>
+        <v>7.641851875437814E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -938,7 +938,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>5.859096374493061E-05</v>
+        <v>5.858753104502324E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -946,7 +946,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.0008151786260164258</v>
+        <v>0.0008151308667133668</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -954,7 +954,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>7.642299618903993E-06</v>
+        <v>7.641851875437814E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -970,7 +970,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.003298926002160223</v>
+        <v>0.003298732726230657</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -978,7 +978,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>5.859096374493061E-05</v>
+        <v>5.858753104502324E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -986,7 +986,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -994,7 +994,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>5.094866412602661E-06</v>
+        <v>5.094567916958543E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001337402433308199</v>
+        <v>0.001337324078201617</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.528459923780799E-05</v>
+        <v>1.528370375087563E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>2.547433206301331E-06</v>
+        <v>2.547283958479271E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -578,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003617143221040565</v>
+        <v>0.0003926909144915533</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -586,7 +586,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001426479016748392</v>
+        <v>0.001452452933728374</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -594,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002114245685537795</v>
+        <v>0.0002089317045051214</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002374068649302681</v>
+        <v>0.002348593738593713</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.273641979239636E-05</v>
+        <v>1.258624725934466E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>8.406037062981596E-05</v>
+        <v>8.306923191167475E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -634,7 +634,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4.839839521110616E-05</v>
+        <v>4.78277395855097E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -642,7 +642,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.037827166783417E-05</v>
+        <v>2.013799561495145E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -650,7 +650,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>4.330382729414762E-05</v>
+        <v>4.78277395855097E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>6.368209896198179E-05</v>
+        <v>6.29312362967233E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -674,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.528370375087563E-05</v>
+        <v>1.762074616308252E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -682,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>3.311469146023053E-05</v>
+        <v>4.531049013364077E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -690,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004116410876902503</v>
+        <v>0.004070392363672063</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -698,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002183022352416736</v>
+        <v>0.00216735177805915</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.0001401006177163599</v>
+        <v>0.0001384487198527913</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -714,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.273641979239636E-05</v>
+        <v>1.258624725934466E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -730,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>5.094567916958543E-05</v>
+        <v>5.034498903737864E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -738,7 +738,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -746,7 +746,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0001579316054257148</v>
+        <v>0.0001887937088901699</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -754,7 +754,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1.273641979239636E-05</v>
+        <v>1.258624725934466E-05</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -762,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.000478889384194103</v>
+        <v>0.0004984153914700485</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -770,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>1.528370375087563E-05</v>
+        <v>1.510349671121359E-05</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -778,7 +778,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -786,7 +786,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>5.094567916958543E-06</v>
+        <v>5.034498903737864E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -794,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006470101254537349</v>
+        <v>0.0006418986102265776</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -802,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.641851875437814E-06</v>
+        <v>7.551748355606795E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -810,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.273641979239636E-05</v>
+        <v>1.762074616308252E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -818,7 +818,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>4.075654333566834E-05</v>
+        <v>4.027599122990291E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -826,7 +826,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.001925746672610329</v>
+        <v>0.001993661565880194</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -834,7 +834,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>2.292555562631344E-05</v>
+        <v>2.768974397055825E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -842,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.001024008151308667</v>
+        <v>0.001039624023621869</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -850,7 +850,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004129147296694899</v>
+        <v>0.004211358332976723</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -858,7 +858,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -882,7 +882,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.0002241609883461759</v>
+        <v>0.0002240352012163349</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -890,7 +890,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>7.641851875437814E-06</v>
+        <v>7.551748355606795E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -898,7 +898,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.528370375087563E-05</v>
+        <v>1.510349671121359E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.001637903585302172</v>
+        <v>0.001643763892070412</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -930,7 +930,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>7.641851875437814E-06</v>
+        <v>7.551748355606795E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -938,7 +938,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>5.858753104502324E-05</v>
+        <v>6.544848574859223E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -946,7 +946,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.0008151308667133668</v>
+        <v>0.0008181060718574028</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -954,7 +954,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>7.641851875437814E-06</v>
+        <v>7.551748355606795E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -970,7 +970,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.003298732726230657</v>
+        <v>0.003305148530303907</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -978,7 +978,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>5.858753104502324E-05</v>
+        <v>6.041398684485436E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -986,7 +986,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -994,7 +994,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>5.094567916958543E-06</v>
+        <v>5.034498903737864E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001337324078201617</v>
+        <v>0.001336659458942403</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.528370375087563E-05</v>
+        <v>1.510349671121359E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>2.547283958479271E-06</v>
+        <v>2.517249451868932E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -578,7 +578,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003926909144915533</v>
+        <v>0.0003924923262718261</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -586,7 +586,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001452452933728374</v>
+        <v>0.001451718411915664</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -594,7 +594,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002089317045051214</v>
+        <v>0.0002088260453882152</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -602,7 +602,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002348593738593713</v>
+        <v>0.002347406028279575</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -610,7 +610,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.258624725934466E-05</v>
+        <v>1.257988225230212E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -626,7 +626,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>8.306923191167475E-05</v>
+        <v>8.302722286519398E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -634,7 +634,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4.78277395855097E-05</v>
+        <v>4.780355255874805E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -642,7 +642,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.013799561495145E-05</v>
+        <v>2.012781160368339E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -650,7 +650,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>4.78277395855097E-05</v>
+        <v>4.780355255874805E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -658,7 +658,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>6.29312362967233E-05</v>
+        <v>6.289941126151059E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -674,7 +674,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.762074616308252E-05</v>
+        <v>1.761183515322297E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -682,7 +682,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>4.531049013364077E-05</v>
+        <v>4.528757610828762E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -690,7 +690,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004070392363672063</v>
+        <v>0.004068333920394505</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -698,7 +698,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.00216735177805915</v>
+        <v>0.002166255723846425</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -706,7 +706,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.0001384487198527913</v>
+        <v>0.0001383787047753233</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -714,7 +714,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.258624725934466E-05</v>
+        <v>1.257988225230212E-05</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -722,7 +722,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -730,7 +730,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>5.034498903737864E-05</v>
+        <v>5.031952900920847E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -738,7 +738,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -746,7 +746,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0001887937088901699</v>
+        <v>0.0001886982337845318</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -754,7 +754,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1.258624725934466E-05</v>
+        <v>1.257988225230212E-05</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -762,7 +762,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004984153914700485</v>
+        <v>0.0004981633371911639</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -770,7 +770,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>1.510349671121359E-05</v>
+        <v>1.509585870276254E-05</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -778,7 +778,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -786,7 +786,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>5.034498903737864E-06</v>
+        <v>5.031952900920848E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -794,7 +794,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006418986102265776</v>
+        <v>0.0006415739948674081</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -802,7 +802,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.551748355606795E-06</v>
+        <v>7.547929351381271E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -810,7 +810,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.762074616308252E-05</v>
+        <v>1.761183515322297E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -818,7 +818,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>4.027599122990291E-05</v>
+        <v>4.025562320736678E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -826,7 +826,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.001993661565880194</v>
+        <v>0.001992653348764656</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -834,7 +834,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>2.768974397055825E-05</v>
+        <v>2.767574095506466E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -842,7 +842,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.001039624023621869</v>
+        <v>0.001039098274040155</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -850,7 +850,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004211358332976723</v>
+        <v>0.004209228601620289</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -858,7 +858,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -882,7 +882,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.0002240352012163349</v>
+        <v>0.0002239219040909777</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -890,7 +890,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>7.551748355606795E-06</v>
+        <v>7.547929351381271E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -898,7 +898,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.510349671121359E-05</v>
+        <v>1.509585870276254E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -914,7 +914,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.001643763892070412</v>
+        <v>0.001642932622150657</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -930,7 +930,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>7.551748355606795E-06</v>
+        <v>7.547929351381271E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -938,7 +938,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>6.544848574859223E-05</v>
+        <v>6.541538771197102E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -946,7 +946,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.0008181060718574028</v>
+        <v>0.0008176923463996377</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -954,7 +954,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>7.551748355606795E-06</v>
+        <v>7.547929351381271E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -970,7 +970,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.003305148530303907</v>
+        <v>0.003303477079454536</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -978,7 +978,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>6.041398684485436E-05</v>
+        <v>6.038343481105017E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -986,7 +986,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -994,7 +994,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>5.034498903737864E-06</v>
+        <v>5.031952900920848E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001336659458942403</v>
+        <v>0.001335983495194485</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.510349671121359E-05</v>
+        <v>1.509585870276254E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>2.517249451868932E-06</v>
+        <v>2.515976450460424E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
   <si>
     <t>defect_desc</t>
   </si>
@@ -197,6 +197,12 @@
   </si>
   <si>
     <t>青/粉斑Mura</t>
+  </si>
+  <si>
+    <t>S向彩色带状Mura</t>
+  </si>
+  <si>
+    <t>S向微亮线</t>
   </si>
 </sst>
 </file>
@@ -554,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -570,7 +576,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -578,7 +584,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003924923262718261</v>
+        <v>0.000316667908501602</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -586,7 +592,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001451718411915664</v>
+        <v>0.001160494747038224</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -594,7 +600,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002088260453882152</v>
+        <v>0.0001974517547127636</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -602,7 +608,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002347406028279575</v>
+        <v>0.002255793159973176</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -610,7 +616,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.257988225230212E-05</v>
+        <v>1.8627524029506E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -626,7 +632,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>8.302722286519398E-05</v>
+        <v>0.0001043141345652336</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -634,7 +640,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4.780355255874805E-05</v>
+        <v>4.470605767081439E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -642,7 +648,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>2.012781160368339E-05</v>
+        <v>1.49020192236048E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -650,7 +656,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>4.780355255874805E-05</v>
+        <v>3.911780046196259E-05</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -658,7 +664,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>6.289941126151059E-05</v>
+        <v>4.6568810073765E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -674,7 +680,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.761183515322297E-05</v>
+        <v>1.30392668206542E-05</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -682,7 +688,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>4.528757610828762E-05</v>
+        <v>3.352954325311079E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -690,7 +696,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004068333920394505</v>
+        <v>0.004109231800909023</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -698,7 +704,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002166255723846425</v>
+        <v>0.002194322330675806</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -706,7 +712,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.0001383787047753233</v>
+        <v>0.0001285299158035914</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -714,7 +720,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>1.257988225230212E-05</v>
+        <v>9.313762014753E-06</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -722,7 +728,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>2.515976450460424E-06</v>
+        <v>5.588257208851799E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -730,7 +736,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>5.031952900920847E-05</v>
+        <v>9.127486774457939E-05</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -738,7 +744,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -746,7 +752,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0001886982337845318</v>
+        <v>0.000139706430221295</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -754,7 +760,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>1.257988225230212E-05</v>
+        <v>9.313762014753E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -762,7 +768,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0004981633371911639</v>
+        <v>0.0003688249757842187</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -770,7 +776,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>1.509585870276254E-05</v>
+        <v>1.11765144177036E-05</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -778,7 +784,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -786,7 +792,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>5.031952900920848E-06</v>
+        <v>3.7255048059012E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -794,7 +800,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0006415739948674081</v>
+        <v>0.001035690336040533</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -802,7 +808,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>7.547929351381271E-06</v>
+        <v>5.588257208851799E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -810,7 +816,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.761183515322297E-05</v>
+        <v>1.30392668206542E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -818,7 +824,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>4.025562320736678E-05</v>
+        <v>3.7255048059012E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -826,7 +832,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.001992653348764656</v>
+        <v>0.001538633484837196</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -834,7 +840,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>2.767574095506466E-05</v>
+        <v>2.04902764324566E-05</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -842,7 +848,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.001039098274040155</v>
+        <v>0.0008158855524923628</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -850,7 +856,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.004209228601620289</v>
+        <v>0.003364130839728783</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -858,7 +864,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -882,7 +888,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.0002239219040909777</v>
+        <v>0.000167647716265554</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -890,7 +896,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>7.547929351381271E-06</v>
+        <v>5.588257208851799E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -898,7 +904,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.509585870276254E-05</v>
+        <v>1.11765144177036E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -914,7 +920,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.001642932622150657</v>
+        <v>0.001220102823932643</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -930,7 +936,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>7.547929351381271E-06</v>
+        <v>5.588257208851799E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -938,7 +944,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>6.541538771197102E-05</v>
+        <v>5.029431487966619E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -946,7 +952,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.0008176923463996377</v>
+        <v>0.000605394530958945</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -954,7 +960,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>7.547929351381271E-06</v>
+        <v>5.588257208851799E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -970,7 +976,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.003303477079454536</v>
+        <v>0.002496088219953804</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -978,7 +984,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>6.038343481105017E-05</v>
+        <v>4.470605767081439E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -986,7 +992,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -994,7 +1000,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1002,7 +1008,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1010,7 +1016,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>5.031952900920848E-06</v>
+        <v>7.451009611802399E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1018,7 +1024,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001335983495194485</v>
+        <v>0.001095298412934953</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1026,7 +1032,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.509585870276254E-05</v>
+        <v>1.30392668206542E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1034,7 +1040,23 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>2.515976450460424E-06</v>
+        <v>1.8627524029506E-06</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B61">
+        <v>1.8627524029506E-06</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>62</v>
+      </c>
+      <c r="B62">
+        <v>1.8627524029506E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>defect_desc</t>
   </si>
@@ -203,6 +203,12 @@
   </si>
   <si>
     <t>S向微亮线</t>
+  </si>
+  <si>
+    <t>R角Mura</t>
+  </si>
+  <si>
+    <t>孔区块状Mura</t>
   </si>
 </sst>
 </file>
@@ -560,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B62"/>
+  <dimension ref="A1:B64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -576,7 +582,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>1.8627524029506E-06</v>
+        <v>3.139623778882577E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -584,7 +590,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.000316667908501602</v>
+        <v>0.0003139623778882577</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -592,7 +598,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.001160494747038224</v>
+        <v>0.002103547931851326</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -600,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0001974517547127636</v>
+        <v>0.0002872755757677558</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -608,7 +614,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002255793159973176</v>
+        <v>0.002116106426966856</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -616,7 +622,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>1.8627524029506E-05</v>
+        <v>4.395473290435607E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -632,7 +638,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>0.0001043141345652336</v>
+        <v>5.494341613044509E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -640,7 +646,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>4.470605767081439E-05</v>
+        <v>3.610567345714963E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -648,7 +654,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1.49020192236048E-05</v>
+        <v>1.883774267329546E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -656,7 +662,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>3.911780046196259E-05</v>
+        <v>0.000800604063615057</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -664,7 +670,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>4.6568810073765E-05</v>
+        <v>2.66868021205019E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -680,7 +686,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>1.30392668206542E-05</v>
+        <v>9.41887133664773E-06</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -688,7 +694,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>3.352954325311079E-05</v>
+        <v>2.982642589938448E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -696,7 +702,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.004109231800909023</v>
+        <v>0.003868016495583334</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -704,7 +710,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002194322330675806</v>
+        <v>0.002273087615910985</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -712,7 +718,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>0.0001285299158035914</v>
+        <v>6.122266368821024E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -720,7 +726,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>9.313762014753E-06</v>
+        <v>9.41887133664773E-06</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -728,7 +734,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>5.588257208851799E-06</v>
+        <v>4.709435668323865E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -736,7 +742,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>9.127486774457939E-05</v>
+        <v>0.0003139623778882577</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -744,7 +750,7 @@
         <v>23</v>
       </c>
       <c r="B23">
-        <v>1.8627524029506E-06</v>
+        <v>1.736825742536426E-06</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -752,7 +758,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.000139706430221295</v>
+        <v>0.0004536756360485323</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -760,7 +766,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>9.313762014753E-06</v>
+        <v>4.709435668323865E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -768,7 +774,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>0.0003688249757842187</v>
+        <v>4.709435668323865E-05</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -776,7 +782,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>1.11765144177036E-05</v>
+        <v>9.41887133664773E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -784,7 +790,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>1.8627524029506E-06</v>
+        <v>4.238492101491479E-05</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -792,7 +798,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>3.7255048059012E-06</v>
+        <v>3.139623778882577E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -800,7 +806,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.001035690336040533</v>
+        <v>0.001251140075884707</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -808,7 +814,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>5.588257208851799E-06</v>
+        <v>9.41887133664773E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -816,7 +822,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.30392668206542E-05</v>
+        <v>1.098868322608902E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -824,7 +830,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>3.7255048059012E-05</v>
+        <v>3.296604967826705E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -832,7 +838,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.001538633484837196</v>
+        <v>0.002398672567066289</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -840,7 +846,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>2.04902764324566E-05</v>
+        <v>4.709435668323865E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -848,7 +854,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0008158855524923628</v>
+        <v>0.0007048455383591385</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -856,7 +862,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.003364130839728783</v>
+        <v>0.00268123870716572</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -864,7 +870,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>1.8627524029506E-06</v>
+        <v>1.569811889441288E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -888,7 +894,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.000167647716265554</v>
+        <v>0.000125584951155303</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -896,7 +902,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>5.588257208851799E-06</v>
+        <v>1.098868322608902E-05</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -904,7 +910,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>1.11765144177036E-05</v>
+        <v>4.709435668323865E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -920,7 +926,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.001220102823932643</v>
+        <v>0.0006357738152237217</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -936,7 +942,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>5.588257208851799E-06</v>
+        <v>6.279247557765153E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -944,7 +950,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>5.029431487966619E-05</v>
+        <v>4.08151091254735E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -952,7 +958,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.000605394530958945</v>
+        <v>0.0005023398046212122</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -960,7 +966,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>5.588257208851799E-06</v>
+        <v>4.709435668323865E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -976,7 +982,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.002496088219953804</v>
+        <v>0.001307653303904593</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -984,7 +990,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>4.470605767081439E-05</v>
+        <v>2.511699023106061E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -992,7 +998,7 @@
         <v>54</v>
       </c>
       <c r="B54">
-        <v>1.8627524029506E-06</v>
+        <v>1.736825742536426E-06</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1000,7 +1006,7 @@
         <v>55</v>
       </c>
       <c r="B55">
-        <v>1.8627524029506E-06</v>
+        <v>1.736825742536426E-06</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1008,7 +1014,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>1.8627524029506E-06</v>
+        <v>3.139623778882577E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1016,7 +1022,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>7.451009611802399E-06</v>
+        <v>7.84905944720644E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1024,7 +1030,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001095298412934953</v>
+        <v>0.0009889814903480116</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1032,7 +1038,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.30392668206542E-05</v>
+        <v>1.255849511553031E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1040,7 +1046,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>1.8627524029506E-06</v>
+        <v>1.569811889441288E-06</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1048,7 +1054,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>1.8627524029506E-06</v>
+        <v>3.139623778882577E-06</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1056,7 +1062,23 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>1.8627524029506E-06</v>
+        <v>1.569811889441288E-06</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>63</v>
+      </c>
+      <c r="B63">
+        <v>7.84905944720644E-06</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64">
+        <v>1.569811889441288E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>defect_desc</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>孔区块状Mura</t>
+  </si>
+  <si>
+    <t>G向粉色带状Mura</t>
   </si>
 </sst>
 </file>
@@ -566,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B64"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -582,7 +585,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>3.139623778882577E-06</v>
+        <v>2.936240994915899E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -590,7 +593,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003139623778882577</v>
+        <v>0.0003215183889432909</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -598,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.002103547931851326</v>
+        <v>0.002492868604683598</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -606,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002872755757677558</v>
+        <v>0.0002965603404865058</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -614,7 +617,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002116106426966856</v>
+        <v>0.00221979819215642</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -622,7 +625,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>4.395473290435607E-05</v>
+        <v>6.312918139069183E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -630,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>8.032438198420501E-07</v>
+        <v>1.468120497457949E-06</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -638,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>5.494341613044509E-05</v>
+        <v>5.578857890340208E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -646,7 +649,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>3.610567345714963E-05</v>
+        <v>3.376677144153283E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -654,7 +657,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1.883774267329546E-05</v>
+        <v>1.908556646695334E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -662,7 +665,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.000800604063615057</v>
+        <v>0.000810402514596788</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -670,7 +673,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>2.66868021205019E-05</v>
+        <v>3.083053044661694E-05</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -686,7 +689,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>9.41887133664773E-06</v>
+        <v>8.808722984747697E-06</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -694,7 +697,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.982642589938448E-05</v>
+        <v>2.936240994915899E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -702,7 +705,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.003868016495583334</v>
+        <v>0.003978606548111043</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -710,7 +713,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002273087615910985</v>
+        <v>0.002335779711455598</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -718,7 +721,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>6.122266368821024E-05</v>
+        <v>7.046978387798157E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -726,7 +729,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>9.41887133664773E-06</v>
+        <v>8.808722984747697E-06</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -734,7 +737,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>4.709435668323865E-06</v>
+        <v>4.404361492373848E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -742,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.0003139623778882577</v>
+        <v>0.0003156459069534591</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -758,7 +761,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0004536756360485323</v>
+        <v>0.0004389680287399269</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -766,7 +769,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>4.709435668323865E-06</v>
+        <v>4.404361492373848E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -774,7 +777,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>4.709435668323865E-05</v>
+        <v>4.404361492373848E-05</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -782,7 +785,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>9.41887133664773E-06</v>
+        <v>8.808722984747697E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -790,7 +793,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>4.238492101491479E-05</v>
+        <v>3.963925343136463E-05</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -798,7 +801,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>3.139623778882577E-06</v>
+        <v>2.936240994915899E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -806,7 +809,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.001251140075884707</v>
+        <v>0.0014035231955698</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -814,7 +817,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>9.41887133664773E-06</v>
+        <v>1.027684348220565E-05</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -822,7 +825,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.098868322608902E-05</v>
+        <v>1.027684348220565E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -830,7 +833,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>3.296604967826705E-05</v>
+        <v>3.083053044661694E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -838,7 +841,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.002398672567066289</v>
+        <v>0.002598573280500571</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -846,7 +849,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>4.709435668323865E-06</v>
+        <v>5.872481989831797E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -854,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0007048455383591385</v>
+        <v>0.0009131709494188445</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -862,7 +865,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.00268123870716572</v>
+        <v>0.003200502684458329</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -870,7 +873,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>1.569811889441288E-06</v>
+        <v>1.468120497457949E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -894,7 +897,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.000125584951155303</v>
+        <v>0.000117449639796636</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -902,7 +905,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>1.098868322608902E-05</v>
+        <v>1.027684348220565E-05</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -910,7 +913,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>4.709435668323865E-06</v>
+        <v>5.872481989831797E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -926,7 +929,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.0006357738152237217</v>
+        <v>0.000610738126942507</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -942,7 +945,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>6.279247557765153E-06</v>
+        <v>5.872481989831797E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -950,7 +953,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>4.08151091254735E-05</v>
+        <v>3.963925343136463E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -958,7 +961,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.0005023398046212122</v>
+        <v>0.000491820366648413</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -966,7 +969,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>4.709435668323865E-06</v>
+        <v>5.872481989831797E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -982,7 +985,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.001307653303904593</v>
+        <v>0.001286073555773164</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -990,7 +993,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>2.511699023106061E-05</v>
+        <v>3.229865094407489E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1014,7 +1017,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>3.139623778882577E-06</v>
+        <v>2.936240994915899E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1022,7 +1025,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>7.84905944720644E-06</v>
+        <v>7.340602487289747E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1030,7 +1033,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.0009889814903480116</v>
+        <v>0.001092281650108714</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1038,7 +1041,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.255849511553031E-05</v>
+        <v>1.174496397966359E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1046,7 +1049,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>1.569811889441288E-06</v>
+        <v>1.468120497457949E-06</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1054,7 +1057,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>3.139623778882577E-06</v>
+        <v>4.404361492373848E-06</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1062,7 +1065,7 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>1.569811889441288E-06</v>
+        <v>1.468120497457949E-06</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1070,7 +1073,7 @@
         <v>63</v>
       </c>
       <c r="B63">
-        <v>7.84905944720644E-06</v>
+        <v>1.321308447712154E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1078,7 +1081,15 @@
         <v>64</v>
       </c>
       <c r="B64">
-        <v>1.569811889441288E-06</v>
+        <v>1.468120497457949E-06</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>65</v>
+      </c>
+      <c r="B65">
+        <v>1.468120497457949E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -585,7 +585,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.936240994915899E-06</v>
+        <v>2.837422768899009E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -593,7 +593,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003215183889432909</v>
+        <v>0.0003163726387322395</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -601,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.002492868604683598</v>
+        <v>0.0017194781979528</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -609,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002965603404865058</v>
+        <v>0.0002879984110432494</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -617,7 +617,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.00221979819215642</v>
+        <v>0.002197583934512283</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -625,7 +625,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>6.312918139069183E-05</v>
+        <v>6.24233009157782E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -633,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1.468120497457949E-06</v>
+        <v>1.418711384449505E-06</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -641,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>5.578857890340208E-05</v>
+        <v>5.391103260908117E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -649,7 +649,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>3.376677144153283E-05</v>
+        <v>3.26303618423386E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -657,7 +657,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1.908556646695334E-05</v>
+        <v>1.844324799784356E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -665,7 +665,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.000810402514596788</v>
+        <v>0.0008171777574429146</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -673,7 +673,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>3.083053044661694E-05</v>
+        <v>0.0001730827889028396</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -689,7 +689,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>8.808722984747697E-06</v>
+        <v>8.512268306697027E-06</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -697,7 +697,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>2.936240994915899E-05</v>
+        <v>3.12116504578891E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -705,7 +705,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.003978606548111043</v>
+        <v>0.003892944038929441</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -713,7 +713,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002335779711455598</v>
+        <v>0.002286962751732601</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -721,7 +721,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>7.046978387798157E-05</v>
+        <v>6.809814645357622E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -729,7 +729,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>8.808722984747697E-06</v>
+        <v>8.512268306697027E-06</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -737,7 +737,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>4.404361492373848E-06</v>
+        <v>4.256134153348514E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.0003156459069534591</v>
+        <v>0.0003106977931944415</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -761,7 +761,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0004389680287399269</v>
+        <v>0.0004298695494881999</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -769,7 +769,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>4.404361492373848E-06</v>
+        <v>4.256134153348514E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -777,7 +777,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>4.404361492373848E-05</v>
+        <v>4.256134153348514E-05</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -785,7 +785,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>8.808722984747697E-06</v>
+        <v>8.512268306697027E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -793,7 +793,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>3.963925343136463E-05</v>
+        <v>3.830520738013662E-05</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -801,7 +801,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>2.936240994915899E-06</v>
+        <v>2.837422768899009E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -809,7 +809,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.0014035231955698</v>
+        <v>0.001387499733991615</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -817,7 +817,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>1.027684348220565E-05</v>
+        <v>9.930979691146531E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -825,7 +825,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.027684348220565E-05</v>
+        <v>1.134969107559604E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -833,7 +833,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>3.083053044661694E-05</v>
+        <v>2.979293907343959E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -841,7 +841,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.002598573280500571</v>
+        <v>0.00289133380150809</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -849,7 +849,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>5.872481989831797E-06</v>
+        <v>7.093556922247523E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.0009131709494188445</v>
+        <v>0.000970398586963461</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -865,7 +865,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.003200502684458329</v>
+        <v>0.003365183403914225</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -873,7 +873,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>1.468120497457949E-06</v>
+        <v>1.418711384449505E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -897,7 +897,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.000117449639796636</v>
+        <v>0.0001390337156760514</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -905,7 +905,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>1.027684348220565E-05</v>
+        <v>9.930979691146531E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -913,7 +913,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>5.872481989831797E-06</v>
+        <v>5.674845537798018E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -929,7 +929,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.000610738126942507</v>
+        <v>0.0005916026473154434</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -945,7 +945,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>5.872481989831797E-06</v>
+        <v>5.674845537798018E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -953,7 +953,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>3.963925343136463E-05</v>
+        <v>3.972391876458612E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -961,7 +961,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.000491820366648413</v>
+        <v>0.0005036425414795741</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -969,7 +969,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>5.872481989831797E-06</v>
+        <v>7.093556922247523E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -985,7 +985,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.001286073555773164</v>
+        <v>0.001255559575237811</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -993,7 +993,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>3.229865094407489E-05</v>
+        <v>3.972391876458612E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1017,7 +1017,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2.936240994915899E-06</v>
+        <v>2.837422768899009E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1025,7 +1025,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>7.340602487289747E-06</v>
+        <v>7.093556922247523E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1033,7 +1033,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001092281650108714</v>
+        <v>0.001136387818944053</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1041,7 +1041,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.174496397966359E-05</v>
+        <v>1.134969107559604E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1049,7 +1049,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>1.468120497457949E-06</v>
+        <v>1.418711384449505E-06</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1057,7 +1057,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>4.404361492373848E-06</v>
+        <v>4.256134153348514E-06</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1065,7 +1065,7 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>1.468120497457949E-06</v>
+        <v>1.418711384449505E-06</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1073,7 +1073,7 @@
         <v>63</v>
       </c>
       <c r="B63">
-        <v>1.321308447712154E-05</v>
+        <v>1.276840246004554E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1081,7 +1081,7 @@
         <v>64</v>
       </c>
       <c r="B64">
-        <v>1.468120497457949E-06</v>
+        <v>1.418711384449505E-06</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>65</v>
       </c>
       <c r="B65">
-        <v>1.468120497457949E-06</v>
+        <v>1.418711384449505E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -585,7 +585,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>2.837422768899009E-06</v>
+        <v>2.835294884844498E-06</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -593,7 +593,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>0.0003163726387322395</v>
+        <v>0.0003161353796601615</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -601,7 +601,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>0.0017194781979528</v>
+        <v>0.001718188700215766</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -609,7 +609,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>0.0002879984110432494</v>
+        <v>0.0002934530205814056</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -617,7 +617,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>0.002197583934512283</v>
+        <v>0.002261147670663487</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -625,7 +625,7 @@
         <v>7</v>
       </c>
       <c r="B7">
-        <v>6.24233009157782E-05</v>
+        <v>6.237648746657896E-05</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -633,7 +633,7 @@
         <v>8</v>
       </c>
       <c r="B8">
-        <v>1.418711384449505E-06</v>
+        <v>1.417647442422249E-06</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -641,7 +641,7 @@
         <v>9</v>
       </c>
       <c r="B9">
-        <v>5.391103260908117E-05</v>
+        <v>5.387060281204547E-05</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -649,7 +649,7 @@
         <v>10</v>
       </c>
       <c r="B10">
-        <v>3.26303618423386E-05</v>
+        <v>3.260589117571173E-05</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -657,7 +657,7 @@
         <v>11</v>
       </c>
       <c r="B11">
-        <v>1.844324799784356E-05</v>
+        <v>1.842941675148924E-05</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -665,7 +665,7 @@
         <v>12</v>
       </c>
       <c r="B12">
-        <v>0.0008171777574429146</v>
+        <v>0.0008165649268352155</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -673,7 +673,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>0.0001730827889028396</v>
+        <v>0.0001729529879755144</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -689,7 +689,7 @@
         <v>15</v>
       </c>
       <c r="B15">
-        <v>8.512268306697027E-06</v>
+        <v>9.923532096955743E-06</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -697,7 +697,7 @@
         <v>16</v>
       </c>
       <c r="B16">
-        <v>3.12116504578891E-05</v>
+        <v>3.118824373328948E-05</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -705,7 +705,7 @@
         <v>17</v>
       </c>
       <c r="B17">
-        <v>0.003892944038929441</v>
+        <v>0.003929718710394475</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -713,7 +713,7 @@
         <v>18</v>
       </c>
       <c r="B18">
-        <v>0.002286962751732601</v>
+        <v>0.002322106510687644</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -721,7 +721,7 @@
         <v>19</v>
       </c>
       <c r="B19">
-        <v>6.809814645357622E-05</v>
+        <v>6.804707723626795E-05</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -729,7 +729,7 @@
         <v>20</v>
       </c>
       <c r="B20">
-        <v>8.512268306697027E-06</v>
+        <v>8.505884654533494E-06</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -737,7 +737,7 @@
         <v>21</v>
       </c>
       <c r="B21">
-        <v>4.256134153348514E-06</v>
+        <v>4.252942327266747E-06</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -745,7 +745,7 @@
         <v>22</v>
       </c>
       <c r="B22">
-        <v>0.0003106977931944415</v>
+        <v>0.0003104647898904726</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -761,7 +761,7 @@
         <v>24</v>
       </c>
       <c r="B24">
-        <v>0.0004298695494881999</v>
+        <v>0.0004295471750539415</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -769,7 +769,7 @@
         <v>25</v>
       </c>
       <c r="B25">
-        <v>4.256134153348514E-06</v>
+        <v>4.252942327266747E-06</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -777,7 +777,7 @@
         <v>26</v>
       </c>
       <c r="B26">
-        <v>4.256134153348514E-05</v>
+        <v>4.252942327266747E-05</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -785,7 +785,7 @@
         <v>27</v>
       </c>
       <c r="B27">
-        <v>8.512268306697027E-06</v>
+        <v>8.505884654533494E-06</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -793,7 +793,7 @@
         <v>28</v>
       </c>
       <c r="B28">
-        <v>3.830520738013662E-05</v>
+        <v>3.827648094540072E-05</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -801,7 +801,7 @@
         <v>29</v>
       </c>
       <c r="B29">
-        <v>2.837422768899009E-06</v>
+        <v>2.835294884844498E-06</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -809,7 +809,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.001387499733991615</v>
+        <v>0.00138645919868896</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -817,7 +817,7 @@
         <v>31</v>
       </c>
       <c r="B31">
-        <v>9.930979691146531E-06</v>
+        <v>9.923532096955743E-06</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -825,7 +825,7 @@
         <v>32</v>
       </c>
       <c r="B32">
-        <v>1.134969107559604E-05</v>
+        <v>1.134117953937799E-05</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -833,7 +833,7 @@
         <v>33</v>
       </c>
       <c r="B33">
-        <v>2.979293907343959E-05</v>
+        <v>2.977059629086723E-05</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -841,7 +841,7 @@
         <v>34</v>
       </c>
       <c r="B34">
-        <v>0.00289133380150809</v>
+        <v>0.002889165487656544</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -849,7 +849,7 @@
         <v>35</v>
       </c>
       <c r="B35">
-        <v>7.093556922247523E-06</v>
+        <v>7.088237212111246E-06</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -857,7 +857,7 @@
         <v>36</v>
       </c>
       <c r="B36">
-        <v>0.000970398586963461</v>
+        <v>0.0009696708506168184</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -865,7 +865,7 @@
         <v>37</v>
       </c>
       <c r="B37">
-        <v>0.003365183403914225</v>
+        <v>0.003366912675752842</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -873,7 +873,7 @@
         <v>38</v>
       </c>
       <c r="B38">
-        <v>1.418711384449505E-06</v>
+        <v>1.417647442422249E-06</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -897,7 +897,7 @@
         <v>41</v>
       </c>
       <c r="B41">
-        <v>0.0001390337156760514</v>
+        <v>0.0001389294493573804</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -905,7 +905,7 @@
         <v>42</v>
       </c>
       <c r="B42">
-        <v>9.930979691146531E-06</v>
+        <v>9.923532096955743E-06</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -913,7 +913,7 @@
         <v>43</v>
       </c>
       <c r="B43">
-        <v>5.674845537798018E-06</v>
+        <v>5.670589769688996E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -929,7 +929,7 @@
         <v>45</v>
       </c>
       <c r="B45">
-        <v>0.0005916026473154434</v>
+        <v>0.0005911589834900778</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -945,7 +945,7 @@
         <v>47</v>
       </c>
       <c r="B47">
-        <v>5.674845537798018E-06</v>
+        <v>5.670589769688996E-06</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -953,7 +953,7 @@
         <v>48</v>
       </c>
       <c r="B48">
-        <v>3.972391876458612E-05</v>
+        <v>3.969412838782297E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -961,7 +961,7 @@
         <v>49</v>
       </c>
       <c r="B49">
-        <v>0.0005036425414795741</v>
+        <v>0.0005032648420598985</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -969,7 +969,7 @@
         <v>50</v>
       </c>
       <c r="B50">
-        <v>7.093556922247523E-06</v>
+        <v>7.088237212111246E-06</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -985,7 +985,7 @@
         <v>52</v>
       </c>
       <c r="B52">
-        <v>0.001255559575237811</v>
+        <v>0.00125461798654369</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -993,7 +993,7 @@
         <v>53</v>
       </c>
       <c r="B53">
-        <v>3.972391876458612E-05</v>
+        <v>3.969412838782297E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1017,7 +1017,7 @@
         <v>56</v>
       </c>
       <c r="B56">
-        <v>2.837422768899009E-06</v>
+        <v>2.835294884844498E-06</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1025,7 +1025,7 @@
         <v>57</v>
       </c>
       <c r="B57">
-        <v>7.093556922247523E-06</v>
+        <v>7.088237212111246E-06</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1033,7 +1033,7 @@
         <v>58</v>
       </c>
       <c r="B58">
-        <v>0.001136387818944053</v>
+        <v>0.001135535601380221</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1041,7 +1041,7 @@
         <v>59</v>
       </c>
       <c r="B59">
-        <v>1.134969107559604E-05</v>
+        <v>1.134117953937799E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1049,7 +1049,7 @@
         <v>60</v>
       </c>
       <c r="B60">
-        <v>1.418711384449505E-06</v>
+        <v>1.417647442422249E-06</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1057,7 +1057,7 @@
         <v>61</v>
       </c>
       <c r="B61">
-        <v>4.256134153348514E-06</v>
+        <v>4.252942327266747E-06</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1065,7 +1065,7 @@
         <v>62</v>
       </c>
       <c r="B62">
-        <v>1.418711384449505E-06</v>
+        <v>1.417647442422249E-06</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1073,7 +1073,7 @@
         <v>63</v>
       </c>
       <c r="B63">
-        <v>1.276840246004554E-05</v>
+        <v>1.275882698180024E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1081,7 +1081,7 @@
         <v>64</v>
       </c>
       <c r="B64">
-        <v>1.418711384449505E-06</v>
+        <v>1.417647442422249E-06</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>65</v>
       </c>
       <c r="B65">
-        <v>1.418711384449505E-06</v>
+        <v>1.417647442422249E-06</v>
       </c>
     </row>
   </sheetData>

--- a/resources/M678/M678_codebaseline.xlsx
+++ b/resources/M678/M678_codebaseline.xlsx
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-18T08:47:33.110787</t>
+          <t>2026-06-18T10:11:12.799685</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>expired_or_legacy</t>
+          <t>multiplier_changed</t>
         </is>
       </c>
     </row>
@@ -1098,6 +1098,18 @@
       <c r="B8" t="inlineStr">
         <is>
           <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>defect_multipliers_signature</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G3亮点=0.2;G向ELA Mura=0;G向单亮线=0.5;G向单暗线=0.8;S向ELA Mura=0;S向亮线=0.7;大面积亮点=0;孔区跑道Mura=5;常亮白斑=0;彩斑Mura=0.2;暗点=0.7;白画面黑斑Mura=3;群亮点=0.3;群暗点=0.8</t>
         </is>
       </c>
     </row>
